--- a/현대로템_분기별_단일판매공급계약_매출인식.xlsx
+++ b/현대로템_분기별_단일판매공급계약_매출인식.xlsx
@@ -8,8 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="계약별_분기매출인식" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="원자료_당기누적" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="안내_분류기준" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="폴란드_방산고객_분기추적" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="원자료_당기누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="안내_분류기준" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="원자료_10%고객" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,11 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="+0.0%;-0.0%;-"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,8 +81,19 @@
       <name val="맑은 고딕"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +135,11 @@
         <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -148,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -222,6 +241,60 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4279,6 +4352,437 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>현대로템 연결 최대고객 = 폴란드(방산)  분기별 매출 추적</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>출처: 연결재무제표 주석 '매출 10% 이상 외부 고객'(2024~ '주요 고객에 대한 공시')  ·  단위: 백만원  ·  폴란드=K2전차(1·2차) 발주처. 단일판매 K2 당기와 정확히 일치 검증됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>보고서</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>폴란드 방산매출
+(당분기 3개월)</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>폴란드 누적
+(YTD/연간)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>전분기比
+(3개월)</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>고객 표기</t>
+        </is>
+      </c>
+      <c r="G3" s="28" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>2023Q2</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="n">
+        <v>241094</v>
+      </c>
+      <c r="D4" s="31" t="n">
+        <v>281269</v>
+      </c>
+      <c r="E4" s="32" t="n"/>
+      <c r="F4" s="29" t="inlineStr">
+        <is>
+          <t>고객2(방산·신규)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>연결매출 10%↑ 첫 등장(K2 폴란드 인도 개시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>2023Q3</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="n">
+        <v>192864</v>
+      </c>
+      <c r="D5" s="31" t="n">
+        <v>474133</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <v>-0.2000470944866455</v>
+      </c>
+      <c r="F5" s="29" t="inlineStr">
+        <is>
+          <t>고객2(방산)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>2023Q4</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>사업(연간)</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="n">
+        <v>198437</v>
+      </c>
+      <c r="D6" s="36" t="n">
+        <v>672570</v>
+      </c>
+      <c r="E6" s="37" t="n">
+        <v>0.02889674876752579</v>
+      </c>
+      <c r="F6" s="34" t="inlineStr">
+        <is>
+          <t>고객2</t>
+        </is>
+      </c>
+      <c r="G6" s="38" t="inlineStr">
+        <is>
+          <t>연간 3개월=연간−9M 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>172704</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>172704</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>-0.1296804422819984</v>
+      </c>
+      <c r="F7" s="29" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>폴란드가 최대고객(고객1)으로 등극</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="n">
+        <v>372423</v>
+      </c>
+      <c r="D8" s="31" t="n">
+        <v>545127</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>1.156427929106012</v>
+      </c>
+      <c r="F8" s="29" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>376120</v>
+      </c>
+      <c r="D9" s="31" t="n">
+        <v>921246</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>0.00992694055621457</v>
+      </c>
+      <c r="F9" s="29" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>2024Q4</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>사업(연간)</t>
+        </is>
+      </c>
+      <c r="C10" s="35" t="n">
+        <v>626674</v>
+      </c>
+      <c r="D10" s="36" t="n">
+        <v>1547921</v>
+      </c>
+      <c r="E10" s="37" t="n">
+        <v>0.6661554866167274</v>
+      </c>
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="G10" s="38" t="inlineStr">
+        <is>
+          <t>연간 3개월=연간−9M 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>466549</v>
+      </c>
+      <c r="D11" s="31" t="n">
+        <v>466549</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <v>-0.2555162700392981</v>
+      </c>
+      <c r="F11" s="29" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="n">
+        <v>514654</v>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>981203</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <v>0.1031094822368399</v>
+      </c>
+      <c r="F12" s="29" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>641284</v>
+      </c>
+      <c r="D13" s="31" t="n">
+        <v>1622487</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>0.2460474976253142</v>
+      </c>
+      <c r="F13" s="29" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>사업(연간)</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="n">
+        <v>579197</v>
+      </c>
+      <c r="D14" s="36" t="n">
+        <v>2201684</v>
+      </c>
+      <c r="E14" s="37" t="n">
+        <v>-0.09681613039141157</v>
+      </c>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="G14" s="38" t="inlineStr">
+        <is>
+          <t>연간 3개월=연간−9M 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>554513</v>
+      </c>
+      <c r="D15" s="31" t="n">
+        <v>554513</v>
+      </c>
+      <c r="E15" s="33" t="n">
+        <v>-0.04261793649655909</v>
+      </c>
+      <c r="F15" s="29" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>※ 연간(FY): 2023 ≈ 6,726억 → 2024 15,479억 → 2025 22,017억 (억원)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:S58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8357,13 +8861,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B24"/>
+  <dimension ref="B1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -8538,7 +9042,1614 @@
         </is>
       </c>
     </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>6. 폴란드(방산 최대고객) 분기 매출 추적 — 시트 [폴란드_방산고객_분기추적]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>· 출처: 연결재무제표 주석 '연결 매출액의 10% 이상 외부 고객'(2024년부터 '주요 고객에 대한 공시'로 서식 변경).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>· 폴란드(K2전차 1·2차 발주처)는 2023년 반기(2Q23)에 방산 신규고객(고객2)으로 처음 10% 이상 등장했고, 2024년부터 연결 최대고객(고객1)입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>· 고객이 익명(고객1·2…)이라, 단일판매 표의 폴란드 K2(1·2차) '당기' 매출과 대조해 식별했습니다 — 값이 정확히 일치함(예: FY24 1,547,921백만원, 2026.1Q 554,513백만원).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>· '당분기 3개월'은 순수 분기 매출입니다. 반기·분기 보고서는 3개월 값을 직접 제공하며, 사업보고서(연간)는 '연간−직전 9개월'로 계산했습니다. (2024·2025 분기합 = 각 연간과 정확히 일치 검증)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>· [원자료_10%고객] 시트: 2021~2026 전 보고서의 10% 이상 고객 전체를 원본 그대로 수록(폴란드 행은 ★ 표시).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>[원자료] 연결 매출 10% 이상 외부 고객 — 보고서별 전체 (단위: 백만원)  ※ 익명 표기(고객1·2…). 폴란드는 위 시트에서 K2와 대조해 식별.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>보고서</t>
+        </is>
+      </c>
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C2" s="39" t="inlineStr">
+        <is>
+          <t>고객</t>
+        </is>
+      </c>
+      <c r="D2" s="39" t="inlineStr">
+        <is>
+          <t>부문</t>
+        </is>
+      </c>
+      <c r="E2" s="39" t="inlineStr">
+        <is>
+          <t>당분기(3개월)</t>
+        </is>
+      </c>
+      <c r="F2" s="39" t="inlineStr">
+        <is>
+          <t>누적/당기(YTD·연간)</t>
+        </is>
+      </c>
+      <c r="G2" s="39" t="inlineStr">
+        <is>
+          <t>각주</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>2021Q2</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C3" s="40" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="E3" s="31" t="n">
+        <v>198226</v>
+      </c>
+      <c r="F3" s="31" t="n">
+        <v>381142</v>
+      </c>
+      <c r="G3" s="29" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr"/>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C4" s="40" t="inlineStr">
+        <is>
+          <t>고객2(*)</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="n">
+        <v>65670</v>
+      </c>
+      <c r="F4" s="31" t="n">
+        <v>140827</v>
+      </c>
+      <c r="G4" s="29" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr"/>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C5" s="40" t="inlineStr">
+        <is>
+          <t>고객3(*)</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="n">
+        <v>77496</v>
+      </c>
+      <c r="F5" s="31" t="n">
+        <v>142615</v>
+      </c>
+      <c r="G5" s="29" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>2021Q3</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>198525</v>
+      </c>
+      <c r="F6" s="31" t="n">
+        <v>579668</v>
+      </c>
+      <c r="G6" s="29" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr"/>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>고객2(*1)</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>135112</v>
+      </c>
+      <c r="F7" s="31" t="n">
+        <v>247975</v>
+      </c>
+      <c r="G7" s="29" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr"/>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="inlineStr">
+        <is>
+          <t>고객3(*1)</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="n">
+        <v>74550</v>
+      </c>
+      <c r="F8" s="31" t="n">
+        <v>215377</v>
+      </c>
+      <c r="G8" s="29" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr"/>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>고객4(*1)</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="n">
+        <v>68566</v>
+      </c>
+      <c r="F9" s="31" t="n">
+        <v>211181</v>
+      </c>
+      <c r="G9" s="29" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr"/>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="inlineStr">
+        <is>
+          <t>고객5(*2)</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="n">
+        <v>55074</v>
+      </c>
+      <c r="F10" s="31" t="n">
+        <v>188680</v>
+      </c>
+      <c r="G10" s="29" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>2021Q4</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>사업</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="n">
+        <v>799475</v>
+      </c>
+      <c r="F11" s="31" t="n">
+        <v>786126</v>
+      </c>
+      <c r="G11" s="29" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr"/>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>사업</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>고객2(*1)</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E12" s="31" t="n">
+        <v>340080</v>
+      </c>
+      <c r="F12" s="31" t="n">
+        <v>79362</v>
+      </c>
+      <c r="G12" s="29" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr"/>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>사업</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="inlineStr">
+        <is>
+          <t>고객3(*1)</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="n">
+        <v>301766</v>
+      </c>
+      <c r="F13" s="31" t="n">
+        <v>236430</v>
+      </c>
+      <c r="G13" s="29" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr"/>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>사업</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="inlineStr">
+        <is>
+          <t>고객4(*2)</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="n">
+        <v>255091</v>
+      </c>
+      <c r="F14" s="31" t="n">
+        <v>285032</v>
+      </c>
+      <c r="G14" s="29" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>2022Q1</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="n">
+        <v>153280</v>
+      </c>
+      <c r="F15" s="31" t="n">
+        <v>182917</v>
+      </c>
+      <c r="G15" s="29" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr"/>
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="inlineStr">
+        <is>
+          <t>고객2</t>
+        </is>
+      </c>
+      <c r="D16" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E16" s="31" t="n">
+        <v>81721</v>
+      </c>
+      <c r="F16" s="31" t="n">
+        <v>75156</v>
+      </c>
+      <c r="G16" s="29" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr"/>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="inlineStr">
+        <is>
+          <t>고객3(*1)</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="n">
+        <v>67449</v>
+      </c>
+      <c r="F17" s="31" t="n">
+        <v>53539</v>
+      </c>
+      <c r="G17" s="29" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr"/>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C18" s="40" t="inlineStr">
+        <is>
+          <t>고객4(*2)</t>
+        </is>
+      </c>
+      <c r="D18" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="n">
+        <v>46454</v>
+      </c>
+      <c r="F18" s="31" t="n">
+        <v>67320</v>
+      </c>
+      <c r="G18" s="29" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="inlineStr"/>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>고객5(*2)</t>
+        </is>
+      </c>
+      <c r="D19" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="n">
+        <v>32949</v>
+      </c>
+      <c r="F19" s="31" t="n">
+        <v>65119</v>
+      </c>
+      <c r="G19" s="29" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>2022Q2</t>
+        </is>
+      </c>
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C20" s="40" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="D20" s="29" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="n">
+        <v>193209</v>
+      </c>
+      <c r="F20" s="31" t="n">
+        <v>346489</v>
+      </c>
+      <c r="G20" s="29" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr"/>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>고객2</t>
+        </is>
+      </c>
+      <c r="D21" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="n">
+        <v>109814</v>
+      </c>
+      <c r="F21" s="31" t="n">
+        <v>191534</v>
+      </c>
+      <c r="G21" s="29" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr"/>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C22" s="40" t="inlineStr">
+        <is>
+          <t>고객3</t>
+        </is>
+      </c>
+      <c r="D22" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="n">
+        <v>85828</v>
+      </c>
+      <c r="F22" s="31" t="n">
+        <v>153276</v>
+      </c>
+      <c r="G22" s="29" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr"/>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="inlineStr">
+        <is>
+          <t>고객4(*2)</t>
+        </is>
+      </c>
+      <c r="D23" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="n">
+        <v>31648</v>
+      </c>
+      <c r="F23" s="31" t="n">
+        <v>78102</v>
+      </c>
+      <c r="G23" s="29" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr"/>
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C24" s="40" t="inlineStr">
+        <is>
+          <t>고객5(*2)</t>
+        </is>
+      </c>
+      <c r="D24" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="n">
+        <v>27409</v>
+      </c>
+      <c r="F24" s="31" t="n">
+        <v>60358</v>
+      </c>
+      <c r="G24" s="29" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>2022Q3</t>
+        </is>
+      </c>
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="D25" s="29" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="n">
+        <v>184732</v>
+      </c>
+      <c r="F25" s="31" t="n">
+        <v>531221</v>
+      </c>
+      <c r="G25" s="29" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr"/>
+      <c r="B26" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C26" s="40" t="inlineStr">
+        <is>
+          <t>고객2</t>
+        </is>
+      </c>
+      <c r="D26" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="n">
+        <v>79697</v>
+      </c>
+      <c r="F26" s="31" t="n">
+        <v>271232</v>
+      </c>
+      <c r="G26" s="29" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr"/>
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C27" s="40" t="inlineStr">
+        <is>
+          <t>고객3</t>
+        </is>
+      </c>
+      <c r="D27" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="n">
+        <v>70318</v>
+      </c>
+      <c r="F27" s="31" t="n">
+        <v>223594</v>
+      </c>
+      <c r="G27" s="29" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="inlineStr"/>
+      <c r="B28" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>고객4(*)</t>
+        </is>
+      </c>
+      <c r="D28" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="n">
+        <v>19275</v>
+      </c>
+      <c r="F28" s="31" t="n">
+        <v>79633</v>
+      </c>
+      <c r="G28" s="29" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>2022Q4</t>
+        </is>
+      </c>
+      <c r="B29" s="29" t="inlineStr">
+        <is>
+          <t>사업</t>
+        </is>
+      </c>
+      <c r="C29" s="40" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="D29" s="29" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="n">
+        <v>743575</v>
+      </c>
+      <c r="F29" s="31" t="n">
+        <v>799475</v>
+      </c>
+      <c r="G29" s="29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="29" t="inlineStr"/>
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>사업</t>
+        </is>
+      </c>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>고객2</t>
+        </is>
+      </c>
+      <c r="D30" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="n">
+        <v>337309</v>
+      </c>
+      <c r="F30" s="31" t="n">
+        <v>301766</v>
+      </c>
+      <c r="G30" s="29" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="inlineStr"/>
+      <c r="B31" s="29" t="inlineStr">
+        <is>
+          <t>사업</t>
+        </is>
+      </c>
+      <c r="C31" s="40" t="inlineStr">
+        <is>
+          <t>고객3(*)</t>
+        </is>
+      </c>
+      <c r="D31" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="n">
+        <v>258233</v>
+      </c>
+      <c r="F31" s="31" t="n">
+        <v>340080</v>
+      </c>
+      <c r="G31" s="29" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>2023Q1</t>
+        </is>
+      </c>
+      <c r="B32" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C32" s="40" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="D32" s="29" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="n">
+        <v>188792</v>
+      </c>
+      <c r="F32" s="31" t="n">
+        <v>153280</v>
+      </c>
+      <c r="G32" s="29" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr"/>
+      <c r="B33" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>고객2(*)</t>
+        </is>
+      </c>
+      <c r="D33" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="n">
+        <v>39542</v>
+      </c>
+      <c r="F33" s="31" t="n">
+        <v>81721</v>
+      </c>
+      <c r="G33" s="29" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="inlineStr"/>
+      <c r="B34" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C34" s="40" t="inlineStr">
+        <is>
+          <t>고객3(*)</t>
+        </is>
+      </c>
+      <c r="D34" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="n">
+        <v>50087</v>
+      </c>
+      <c r="F34" s="31" t="n">
+        <v>67449</v>
+      </c>
+      <c r="G34" s="29" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>2023Q2</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C35" s="40" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="D35" s="29" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="E35" s="31" t="n">
+        <v>193363</v>
+      </c>
+      <c r="F35" s="31" t="n">
+        <v>382155</v>
+      </c>
+      <c r="G35" s="29" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="41" t="inlineStr"/>
+      <c r="B36" s="41" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C36" s="42" t="inlineStr">
+        <is>
+          <t>고객2(*1) ★폴란드</t>
+        </is>
+      </c>
+      <c r="D36" s="41" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="E36" s="43" t="n">
+        <v>241094</v>
+      </c>
+      <c r="F36" s="43" t="n">
+        <v>281269</v>
+      </c>
+      <c r="G36" s="41" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="inlineStr"/>
+      <c r="B37" s="29" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C37" s="40" t="inlineStr">
+        <is>
+          <t>고객3(*2)</t>
+        </is>
+      </c>
+      <c r="D37" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="n">
+        <v>21133</v>
+      </c>
+      <c r="F37" s="31" t="n">
+        <v>60675</v>
+      </c>
+      <c r="G37" s="29" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="29" t="inlineStr"/>
+      <c r="B38" s="29" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C38" s="40" t="inlineStr">
+        <is>
+          <t>고객4(*2)</t>
+        </is>
+      </c>
+      <c r="D38" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E38" s="31" t="n">
+        <v>59133</v>
+      </c>
+      <c r="F38" s="31" t="n">
+        <v>109220</v>
+      </c>
+      <c r="G38" s="29" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="29" t="inlineStr">
+        <is>
+          <t>2023Q3</t>
+        </is>
+      </c>
+      <c r="B39" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C39" s="40" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="D39" s="29" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="E39" s="31" t="n">
+        <v>186203</v>
+      </c>
+      <c r="F39" s="31" t="n">
+        <v>568359</v>
+      </c>
+      <c r="G39" s="29" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="41" t="inlineStr"/>
+      <c r="B40" s="41" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C40" s="42" t="inlineStr">
+        <is>
+          <t>고객2(*1) ★폴란드</t>
+        </is>
+      </c>
+      <c r="D40" s="41" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="E40" s="43" t="n">
+        <v>192864</v>
+      </c>
+      <c r="F40" s="43" t="n">
+        <v>474133</v>
+      </c>
+      <c r="G40" s="41" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="inlineStr"/>
+      <c r="B41" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C41" s="40" t="inlineStr">
+        <is>
+          <t>고객3(*2)</t>
+        </is>
+      </c>
+      <c r="D41" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E41" s="31" t="n">
+        <v>4483</v>
+      </c>
+      <c r="F41" s="31" t="n">
+        <v>65158</v>
+      </c>
+      <c r="G41" s="29" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="29" t="inlineStr"/>
+      <c r="B42" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C42" s="40" t="inlineStr">
+        <is>
+          <t>고객4(*2)</t>
+        </is>
+      </c>
+      <c r="D42" s="29" t="inlineStr">
+        <is>
+          <t>철도</t>
+        </is>
+      </c>
+      <c r="E42" s="31" t="n">
+        <v>70884</v>
+      </c>
+      <c r="F42" s="31" t="n">
+        <v>180104</v>
+      </c>
+      <c r="G42" s="29" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>2023Q4</t>
+        </is>
+      </c>
+      <c r="B43" s="29" t="inlineStr">
+        <is>
+          <t>사업</t>
+        </is>
+      </c>
+      <c r="C43" s="40" t="inlineStr">
+        <is>
+          <t>고객1</t>
+        </is>
+      </c>
+      <c r="D43" s="29" t="inlineStr"/>
+      <c r="E43" s="44" t="n"/>
+      <c r="F43" s="31" t="n">
+        <v>742147</v>
+      </c>
+      <c r="G43" s="29" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="41" t="inlineStr"/>
+      <c r="B44" s="41" t="inlineStr">
+        <is>
+          <t>사업</t>
+        </is>
+      </c>
+      <c r="C44" s="42" t="inlineStr">
+        <is>
+          <t>고객2 ★폴란드</t>
+        </is>
+      </c>
+      <c r="D44" s="41" t="inlineStr"/>
+      <c r="E44" s="45" t="n"/>
+      <c r="F44" s="43" t="n">
+        <v>672570</v>
+      </c>
+      <c r="G44" s="41" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="29" t="inlineStr"/>
+      <c r="B45" s="29" t="inlineStr">
+        <is>
+          <t>사업</t>
+        </is>
+      </c>
+      <c r="C45" s="40" t="inlineStr">
+        <is>
+          <t>고객3</t>
+        </is>
+      </c>
+      <c r="D45" s="29" t="inlineStr"/>
+      <c r="E45" s="44" t="n"/>
+      <c r="F45" s="31" t="n">
+        <v>70190</v>
+      </c>
+      <c r="G45" s="29" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="41" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="B46" s="41" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C46" s="42" t="inlineStr">
+        <is>
+          <t>고객1 ★폴란드</t>
+        </is>
+      </c>
+      <c r="D46" s="41" t="inlineStr"/>
+      <c r="E46" s="45" t="n"/>
+      <c r="F46" s="43" t="n">
+        <v>172704</v>
+      </c>
+      <c r="G46" s="41" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr"/>
+      <c r="B47" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C47" s="40" t="inlineStr">
+        <is>
+          <t>고객2</t>
+        </is>
+      </c>
+      <c r="D47" s="29" t="inlineStr"/>
+      <c r="E47" s="44" t="n"/>
+      <c r="F47" s="31" t="n">
+        <v>109849</v>
+      </c>
+      <c r="G47" s="29" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="41" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="B48" s="41" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C48" s="42" t="inlineStr">
+        <is>
+          <t>고객1 ★폴란드</t>
+        </is>
+      </c>
+      <c r="D48" s="41" t="inlineStr"/>
+      <c r="E48" s="43" t="n">
+        <v>372423</v>
+      </c>
+      <c r="F48" s="43" t="n">
+        <v>545127</v>
+      </c>
+      <c r="G48" s="41" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="29" t="inlineStr"/>
+      <c r="B49" s="29" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C49" s="40" t="inlineStr">
+        <is>
+          <t>고객2</t>
+        </is>
+      </c>
+      <c r="D49" s="29" t="inlineStr"/>
+      <c r="E49" s="31" t="n">
+        <v>153293</v>
+      </c>
+      <c r="F49" s="31" t="n">
+        <v>263142</v>
+      </c>
+      <c r="G49" s="29" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="41" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="B50" s="41" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C50" s="42" t="inlineStr">
+        <is>
+          <t>고객1 ★폴란드</t>
+        </is>
+      </c>
+      <c r="D50" s="41" t="inlineStr"/>
+      <c r="E50" s="43" t="n">
+        <v>376120</v>
+      </c>
+      <c r="F50" s="43" t="n">
+        <v>921246</v>
+      </c>
+      <c r="G50" s="41" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr"/>
+      <c r="B51" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C51" s="40" t="inlineStr">
+        <is>
+          <t>고객2</t>
+        </is>
+      </c>
+      <c r="D51" s="29" t="inlineStr"/>
+      <c r="E51" s="31" t="n">
+        <v>139385</v>
+      </c>
+      <c r="F51" s="31" t="n">
+        <v>402527</v>
+      </c>
+      <c r="G51" s="29" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="41" t="inlineStr">
+        <is>
+          <t>2024Q4</t>
+        </is>
+      </c>
+      <c r="B52" s="41" t="inlineStr">
+        <is>
+          <t>사업</t>
+        </is>
+      </c>
+      <c r="C52" s="42" t="inlineStr">
+        <is>
+          <t>고객1 ★폴란드</t>
+        </is>
+      </c>
+      <c r="D52" s="41" t="inlineStr"/>
+      <c r="E52" s="45" t="n"/>
+      <c r="F52" s="43" t="n">
+        <v>1547921</v>
+      </c>
+      <c r="G52" s="41" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="29" t="inlineStr"/>
+      <c r="B53" s="29" t="inlineStr">
+        <is>
+          <t>사업</t>
+        </is>
+      </c>
+      <c r="C53" s="40" t="inlineStr">
+        <is>
+          <t>고객2</t>
+        </is>
+      </c>
+      <c r="D53" s="29" t="inlineStr"/>
+      <c r="E53" s="44" t="n"/>
+      <c r="F53" s="31" t="n">
+        <v>621023</v>
+      </c>
+      <c r="G53" s="29" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="41" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="B54" s="41" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C54" s="42" t="inlineStr">
+        <is>
+          <t>고객1 ★폴란드</t>
+        </is>
+      </c>
+      <c r="D54" s="41" t="inlineStr"/>
+      <c r="E54" s="45" t="n"/>
+      <c r="F54" s="43" t="n">
+        <v>466549</v>
+      </c>
+      <c r="G54" s="41" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="29" t="inlineStr"/>
+      <c r="B55" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C55" s="40" t="inlineStr">
+        <is>
+          <t>고객2</t>
+        </is>
+      </c>
+      <c r="D55" s="29" t="inlineStr"/>
+      <c r="E55" s="44" t="n"/>
+      <c r="F55" s="31" t="n">
+        <v>160246</v>
+      </c>
+      <c r="G55" s="29" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="41" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="B56" s="41" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C56" s="42" t="inlineStr">
+        <is>
+          <t>고객1 ★폴란드</t>
+        </is>
+      </c>
+      <c r="D56" s="41" t="inlineStr"/>
+      <c r="E56" s="43" t="n">
+        <v>514654</v>
+      </c>
+      <c r="F56" s="43" t="n">
+        <v>981203</v>
+      </c>
+      <c r="G56" s="41" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="29" t="inlineStr"/>
+      <c r="B57" s="29" t="inlineStr">
+        <is>
+          <t>반기</t>
+        </is>
+      </c>
+      <c r="C57" s="40" t="inlineStr">
+        <is>
+          <t>고객2</t>
+        </is>
+      </c>
+      <c r="D57" s="29" t="inlineStr"/>
+      <c r="E57" s="31" t="n">
+        <v>207609</v>
+      </c>
+      <c r="F57" s="31" t="n">
+        <v>367855</v>
+      </c>
+      <c r="G57" s="29" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="41" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="B58" s="41" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C58" s="42" t="inlineStr">
+        <is>
+          <t>고객1 ★폴란드</t>
+        </is>
+      </c>
+      <c r="D58" s="41" t="inlineStr"/>
+      <c r="E58" s="43" t="n">
+        <v>641284</v>
+      </c>
+      <c r="F58" s="43" t="n">
+        <v>1622487</v>
+      </c>
+      <c r="G58" s="41" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="29" t="inlineStr"/>
+      <c r="B59" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C59" s="40" t="inlineStr">
+        <is>
+          <t>고객2</t>
+        </is>
+      </c>
+      <c r="D59" s="29" t="inlineStr"/>
+      <c r="E59" s="31" t="n">
+        <v>192082</v>
+      </c>
+      <c r="F59" s="31" t="n">
+        <v>559937</v>
+      </c>
+      <c r="G59" s="29" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="41" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+      <c r="B60" s="41" t="inlineStr">
+        <is>
+          <t>사업</t>
+        </is>
+      </c>
+      <c r="C60" s="42" t="inlineStr">
+        <is>
+          <t>고객1 ★폴란드</t>
+        </is>
+      </c>
+      <c r="D60" s="41" t="inlineStr"/>
+      <c r="E60" s="45" t="n"/>
+      <c r="F60" s="43" t="n">
+        <v>2201684</v>
+      </c>
+      <c r="G60" s="41" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="29" t="inlineStr"/>
+      <c r="B61" s="29" t="inlineStr">
+        <is>
+          <t>사업</t>
+        </is>
+      </c>
+      <c r="C61" s="40" t="inlineStr">
+        <is>
+          <t>고객2</t>
+        </is>
+      </c>
+      <c r="D61" s="29" t="inlineStr"/>
+      <c r="E61" s="44" t="n"/>
+      <c r="F61" s="31" t="n">
+        <v>744376</v>
+      </c>
+      <c r="G61" s="29" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="41" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="B62" s="41" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C62" s="42" t="inlineStr">
+        <is>
+          <t>고객1 ★폴란드</t>
+        </is>
+      </c>
+      <c r="D62" s="41" t="inlineStr"/>
+      <c r="E62" s="45" t="n"/>
+      <c r="F62" s="43" t="n">
+        <v>554513</v>
+      </c>
+      <c r="G62" s="41" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr"/>
+      <c r="B63" s="29" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C63" s="40" t="inlineStr">
+        <is>
+          <t>고객2</t>
+        </is>
+      </c>
+      <c r="D63" s="29" t="inlineStr"/>
+      <c r="E63" s="44" t="n"/>
+      <c r="F63" s="31" t="n">
+        <v>181539</v>
+      </c>
+      <c r="G63" s="29" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>